--- a/branches/master/all-profiles.xlsx
+++ b/branches/master/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T16:29:24+00:00</t>
+    <t>2026-09-02T07:15:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/all-profiles.xlsx
+++ b/branches/master/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T07:15:34+00:00</t>
+    <t>2026-09-02T11:58:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/all-profiles.xlsx
+++ b/branches/master/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0</t>
+    <t>2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T11:58:19+00:00</t>
+    <t>2026-09-02T12:35:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/all-profiles.xlsx
+++ b/branches/master/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T12:35:29+00:00</t>
+    <t>2026-09-02T13:24:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/all-profiles.xlsx
+++ b/branches/master/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T15:00:33+00:00</t>
+    <t>2026-09-02T15:34:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/all-profiles.xlsx
+++ b/branches/master/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T15:34:02+00:00</t>
+    <t>2026-09-02T17:45:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/all-profiles.xlsx
+++ b/branches/master/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T17:45:23+00:00</t>
+    <t>2026-09-02T17:52:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/all-profiles.xlsx
+++ b/branches/master/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot.rc2</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T17:52:09+00:00</t>
+    <t>2026-09-02T18:06:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2630,6 +2630,10 @@
     <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections|4.0.1</t>
   </si>
   <si>
+    <t xml:space="preserve">pattern:coding}
+</t>
+  </si>
+  <si>
     <t>DiagnosticReport.category:laborbefund</t>
   </si>
   <si>
@@ -2640,14 +2644,6 @@
   </si>
   <si>
     <t>Die verpflichtende Kategorie des Laborbefunds. Weitere Kategorien, etwa der Laborbereich, sind als zusaetzliche category-Eintraege zulaessig.</t>
-  </si>
-  <si>
-    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
-  &lt;coding&gt;
-    &lt;system value="http://loinc.org"/&gt;
-    &lt;code value="26436-6"/&gt;
-  &lt;/coding&gt;
-&lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
     <t>DiagnosticReport.category:laborbefund.id</t>
@@ -35024,7 +35020,7 @@
         <v>77</v>
       </c>
       <c r="AC280" t="s" s="2">
-        <v>544</v>
+        <v>840</v>
       </c>
       <c r="AD280" s="2"/>
       <c r="AE280" t="s" s="2">
@@ -35054,13 +35050,13 @@
         <v>737</v>
       </c>
       <c r="B281" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="C281" t="s" s="2">
         <v>834</v>
       </c>
       <c r="D281" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="E281" t="s" s="2">
         <v>835</v>
@@ -35085,10 +35081,10 @@
         <v>422</v>
       </c>
       <c r="M281" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="N281" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="O281" t="s" s="2">
         <v>837</v>
@@ -35102,7 +35098,7 @@
         <v>77</v>
       </c>
       <c r="T281" t="s" s="2">
-        <v>844</v>
+        <v>77</v>
       </c>
       <c r="U281" t="s" s="2">
         <v>77</v>
@@ -47951,7 +47947,7 @@
         <v>77</v>
       </c>
       <c r="AC403" t="s" s="2">
-        <v>544</v>
+        <v>840</v>
       </c>
       <c r="AD403" s="2"/>
       <c r="AE403" t="s" s="2">
@@ -49190,7 +49186,7 @@
         <v>77</v>
       </c>
       <c r="T415" t="s" s="2">
-        <v>844</v>
+        <v>77</v>
       </c>
       <c r="U415" t="s" s="2">
         <v>77</v>

--- a/branches/master/all-profiles.xlsx
+++ b/branches/master/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T20:13:51+00:00</t>
+    <t>2026-09-08T09:14:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/all-profiles.xlsx
+++ b/branches/master/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T09:14:04+00:00</t>
+    <t>2026-09-08T11:22:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/all-profiles.xlsx
+++ b/branches/master/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc3</t>
+    <t>2027.0.0-ballot.rc4</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T11:22:39+00:00</t>
+    <t>2026-09-08T11:59:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
